--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -619,7 +619,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -276,7 +276,7 @@
 【JP Core仕様】画像結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -846,6 +846,15 @@
     <t>レポートを作成した臨床分野・部門、または診断サービス（CT, US, MRIなど）を分類するコード。 これは、検索、並べ替え、および表示の目的で使用される。【JP-Core仕様】放射線レポートは第1コードとして LP29684-5 を固定値として設定。第2コード以下にDICOMModalityコードを列挙することでレポートの対象検査内容を示す。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP29684-5"/&gt;
+    &lt;display value="放射線"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -867,16 +876,10 @@
     <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.coding.version</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP29684-5</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -1123,10 +1126,10 @@
 </t>
   </si>
   <si>
-    <t>診断レポートが関係するヘルスケアイベントに関する情報</t>
-  </si>
-  <si>
-    <t>この診断レポートが関するヘルスケアイベント。</t>
+    <t>診断レポートが関係する診療イベントに関する情報</t>
+  </si>
+  <si>
+    <t>この診断レポートが関する診療イベント。</t>
   </si>
   <si>
     <t>これは通常、レポートの作成が発生するEncounterだが、一部のイベントはEncounterの正式な完了の前または後に開始される場合がある（例えば入院前の検査）。その場合でも（入院に関連して検査が行われる場合など）、Encounterのコンテキストに関連付けられる。  
@@ -4786,7 +4789,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4805,7 +4808,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4852,7 +4855,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>195</v>
@@ -4964,7 +4967,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>201</v>
@@ -5078,7 +5081,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>206</v>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>215</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>216</v>
@@ -5420,7 +5423,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>217</v>
@@ -5465,7 +5468,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5693,7 +5696,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>237</v>
@@ -5878,7 +5881,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>243</v>
@@ -5994,7 +5997,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>252</v>
@@ -6110,13 +6113,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>182</v>
@@ -6141,10 +6144,10 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>186</v>
@@ -6177,7 +6180,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6224,7 +6227,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>195</v>
@@ -6336,7 +6339,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>201</v>
@@ -6450,7 +6453,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>206</v>
@@ -6566,7 +6569,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>215</v>
@@ -6678,7 +6681,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>216</v>
@@ -6792,7 +6795,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>217</v>
@@ -6837,7 +6840,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>81</v>
@@ -6908,7 +6911,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>224</v>
@@ -7022,7 +7025,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>231</v>
@@ -7051,10 +7054,10 @@
         <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7136,7 +7139,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>237</v>
@@ -7165,10 +7168,10 @@
         <v>196</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -7250,7 +7253,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>243</v>
@@ -7366,7 +7369,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>252</v>
@@ -7482,14 +7485,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7511,13 +7514,13 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7547,7 +7550,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7565,7 +7568,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -7580,24 +7583,24 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7706,10 +7709,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7820,10 +7823,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7895,7 +7898,7 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -7934,13 +7937,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>81</v>
@@ -7965,13 +7968,13 @@
         <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>211</v>
@@ -8052,10 +8055,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8164,10 +8167,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8278,10 +8281,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8307,10 +8310,10 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>219</v>
@@ -8323,7 +8326,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>81</v>
@@ -8394,10 +8397,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8508,10 +8511,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8537,10 +8540,10 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -8551,7 +8554,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>81</v>
@@ -8622,10 +8625,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8651,10 +8654,10 @@
         <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
@@ -8668,7 +8671,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -8736,10 +8739,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8852,10 +8855,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8968,14 +8971,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8994,19 +8997,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9055,7 +9058,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9070,28 +9073,28 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9110,19 +9113,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9171,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9186,28 +9189,28 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9226,19 +9229,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9287,7 +9290,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9302,28 +9305,28 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9342,19 +9345,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9403,7 +9406,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9421,25 +9424,25 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9458,19 +9461,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9519,7 +9522,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9534,28 +9537,28 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9574,19 +9577,19 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="O68" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9635,7 +9638,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9650,24 +9653,24 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9690,19 +9693,19 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9751,7 +9754,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9769,10 +9772,10 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -9780,14 +9783,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9806,19 +9809,19 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -9867,7 +9870,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9885,10 +9888,10 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -9896,10 +9899,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9922,16 +9925,16 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9981,7 +9984,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10002,7 +10005,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10010,14 +10013,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10036,19 +10039,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10097,7 +10100,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10115,10 +10118,10 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10126,10 +10129,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10238,10 +10241,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10352,14 +10355,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10381,10 +10384,10 @@
         <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>140</v>
@@ -10439,7 +10442,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10468,10 +10471,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10497,16 +10500,16 @@
         <v>196</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -10555,7 +10558,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10576,7 +10579,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -10584,10 +10587,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10610,16 +10613,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10669,7 +10672,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>91</v>
@@ -10690,7 +10693,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -10698,14 +10701,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10727,16 +10730,16 @@
         <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -10785,7 +10788,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10803,10 +10806,10 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -10814,10 +10817,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10843,13 +10846,13 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10878,11 +10881,11 @@
         <v>187</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z79" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
       </c>
@@ -10899,7 +10902,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10917,10 +10920,10 @@
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -10928,10 +10931,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10954,19 +10957,19 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11015,7 +11018,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11033,10 +11036,10 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -399,7 +399,7 @@
     <t>人が読める形式で提示された情報。放射線レポートの場合はレポートの所見が保持される【詳細参照】</t>
   </si>
   <si>
-    <t>リソースの概要を含み、リソースの内容を人間が解釈できる形で表現するために用いられる。すべての構造化データをエンコードする必要はないが、人間がテキストを読むだけで「臨床的に安全」になるように十分な詳細を含める必要がある。リソース定義は、臨床的安全性を確保するために、テキストの中でどのコンテンツを表現すべきかを定義することができる。放射線レポートでは少なくともレポートの所見が格納されることが期待される。また，検索可能な文字列が存在する部位としても利用されることを想定している。</t>
+    <t>リソースの概要を含み、リソースの内容を人間が解釈できる形で表現するために用いられる。すべての構造化データをエンコードする必要はないが、人間がテキストを読むだけで「臨床的に安全」になるように十分な詳細を含める必要がある。リソース定義は、臨床的安全性を確保するために、テキストの中でどのコンテンツを表現すべきかを定義することができる。放射線レポートでは少なくともレポートの所見が格納されることが期待される。また、検索可能な文字列が存在する部位としても利用されることを想定している。</t>
   </si>
   <si>
     <t>放射線レポートの場合、主となる所見を表すエレメントは他のリソースエレメントには存在しない。よってこのドメインリソースを用いてレポートの少なくとも「所見」を人間が可読な状態で保持することが求められる。</t>
@@ -498,7 +498,7 @@
     <t>実行者または他のシステムによってこのレポートに割り当てられた識別子。</t>
   </si>
   <si>
-    <t>通常は診断サービスプロバイダの情報システムにより設定される。  
+    <t>通常は診断サービスプロバイダーの情報システムにより設定される。  
 【JP Core仕様】レポート番号  
 （放射線情報システム(RIS)による発番が想定されるが、施設によって電子カルテ等のオーダ番号を使う場合もあり得る）</t>
   </si>
@@ -961,7 +961,7 @@
     <t>この診断レポートを表現するコードや名称</t>
   </si>
   <si>
-    <t>【JP Core仕様】[画像診断レポート交換手順ガイドライン](https://www.jira-net.or.jp/publishing/files/jesra/JESRA_TR-0042_2018.pdf)「5.1 レポート種別コード」に記載されているLOINCコード [Diagnostic imaging study](https://loinc.org/18748-4/) を指定。コードを指定できない場合はCodeableConceptを使用せずテキスト等を直接コーディングすることも許容されるが、要素間の調整と事前・事後の内容の整合性確保のために独自の構造を提供する必要があるので留意すること。</t>
+    <t>【JP Core仕様】[画像診断レポート交換手順ガイドライン](https://www.jira-net.or.jp/publishing/files/jesra/JESRA_TR-0042_2018.pdf)「5.1 レポート種別コード」に記載されているLOINCコード [Diagnostic imaging study](https://loinc.org/18748-4/) を指定。コードを指定できない場合はCodeableConceptを使用せずテキスト等を直接コード化することも許容されるが、要素間の調整と事前・事後の内容の整合性確保のために独自の構造を提供する必要があるので留意すること。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
@@ -1202,7 +1202,7 @@
     <t>このバージョンの診断レポートが医療者に提供/確定された日時</t>
   </si>
   <si>
-    <t>このバージョンのレポートがプロバイダに提供された日時。通常、レポートがレビューおよび検証された後になる。</t>
+    <t>このバージョンのレポートがプロバイダーに提供された日時。通常、レポートがレビューおよび検証された後になる。</t>
   </si>
   <si>
     <t>リソース自体の更新時間とは異なる場合がある。これは、レポートの実際のリリース時間ではなく、レコード（場合によってはセカンダリコピー）のステータスであるため。  
@@ -1476,7 +1476,7 @@
     <t>診断レポートの要約の結論 (interpretation/impression) を表す 1 つ以上のコード。</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。 場合によっては、モデルにcodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と事前調整および事後調整を管理するための独自の構造を提供する必要がある。   
+    <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。 場合によっては、モデルにcodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と事前調整および事後調整を管理するための独自の構造を提供する必要がある。   
 【JP Core仕様】・放射線レポートの所見の結論となるコードを設定。  
 ・例えば、ICD 病名コード</t>
   </si>
